--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08169</v>
+        <v>0.08517</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04607</v>
+        <v>0.05448</v>
       </c>
       <c r="E2" t="n">
         <v>0.099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09702</v>
+        <v>0.10098</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.08225</v>
+        <v>0.07803</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03779</v>
+        <v>0.03498</v>
       </c>
       <c r="E3" t="n">
         <v>0.0984</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04482</v>
+        <v>0.04518</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -565,13 +565,13 @@
         <v>0.05734</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01866</v>
+        <v>0.02333</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.058</v>
+        <v>0.06335</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -592,16 +592,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07417</v>
+        <v>0.06852</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02248</v>
+        <v>0.02192</v>
       </c>
       <c r="E5" t="n">
         <v>0.08989999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03371</v>
+        <v>0.0309</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -626,13 +626,13 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.0738625</v>
+        <v>0.072265</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00010117686875</v>
+        <v>0.000109138725</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01005867132130283</v>
+        <v>0.01044694811894843</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -685,13 +685,13 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.02245166666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002999847222222222</v>
+        <v>0.0003653303472222222</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01732006703861801</v>
+        <v>0.01911361680117665</v>
       </c>
     </row>
     <row r="9">
@@ -713,13 +713,13 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.03892499999999999</v>
+        <v>0.04006833333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001138523858333333</v>
+        <v>0.001262232880555556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03374201917984952</v>
+        <v>0.03552791691832714</v>
       </c>
     </row>
     <row r="10">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.06832000000000001</v>
+        <v>0.06387</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05545</v>
+        <v>0.05544</v>
       </c>
       <c r="E10" t="n">
         <v>0.099</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09801</v>
+        <v>0.10395</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.09068999999999999</v>
+        <v>0.08892</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0355</v>
+        <v>0.03215</v>
       </c>
       <c r="E11" t="n">
         <v>0.0984</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04569</v>
+        <v>0.04499</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.11133</v>
+        <v>0.10801</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03599</v>
+        <v>0.04134</v>
       </c>
       <c r="E12" t="n">
         <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06399000000000001</v>
+        <v>0.06533</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -824,16 +824,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.12304</v>
+        <v>0.11012</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03706</v>
+        <v>0.04607</v>
       </c>
       <c r="E13" t="n">
         <v>0.08989999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03482</v>
+        <v>0.02866</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -858,13 +858,13 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.09834499999999999</v>
+        <v>0.09272999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0004346382249999999</v>
+        <v>0.00034582655</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02084797891883048</v>
+        <v>0.01859641228839585</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -917,13 +917,13 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>0.02733333333333333</v>
+        <v>0.02916666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0004201682555555556</v>
+        <v>0.000472414988888889</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02049800613609908</v>
+        <v>0.02173510958999032</v>
       </c>
     </row>
     <row r="17">
@@ -945,13 +945,13 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>0.04041833333333333</v>
+        <v>0.04048833333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001199806447222222</v>
+        <v>0.001347212713888889</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03463822234500816</v>
+        <v>0.03670439638366076</v>
       </c>
     </row>
   </sheetData>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,59 +441,114 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>original error rate PC_LabelCorrection</t>
+          <t>taxa_de_erro_detectada_corretamente_mean</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>error rate after correction PC_LabelCorrection</t>
+          <t>taxa_de_erro_detectada_corretamente_variance</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>original error rate CL</t>
+          <t>taxa_de_erro_detectada_corretamente_std</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>error rate after correction CL</t>
+          <t>taxa_de_erro_detectada_erradamente_mean</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>before_fix_mean</t>
+          <t>taxa_de_erro_detectada_erradamente_variance</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_fix_variance</t>
+          <t>taxa_de_erro_detectada_erradamente_std</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>before_fix_std</t>
+          <t>erros_de_rotulo_ajustados_corretamente_mean</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>after_fix_mean</t>
+          <t>erros_de_rotulo_ajustados_corretamente_variance</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>after_fix_variance</t>
+          <t>erros_de_rotulo_ajustados_corretamente_std</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>after_fix_std</t>
+          <t>taxa_do_erro_ajustada_corretamente_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_do_erro_ajustada_corretamente_variance</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_do_erro_ajustada_corretamente_std</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_do_erro_nao_corrigida_mean</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_do_erro_nao_corrigida_variance</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_do_erro_nao_corrigida_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>novos_erros_gerados_mean</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>novos_erros_gerados_variance</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>novos_erros_gerados_std</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_de_erro_novos_erros_gerados_com_relacao_ao_dataset_original_mean</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_de_erro_novos_erros_gerados_com_relacao_ao_dataset_original_variance</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>taxa_de_erro_novos_erros_gerados_com_relacao_ao_dataset_original_std</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>metric_2D</t>
+          <t>ocpc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -502,28 +557,73 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08517</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05448</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.10098</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>0.08415841584158416</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>metric_breast_cancer</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -532,426 +632,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07803</v>
+        <v>0.04950495049504951</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03498</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0984</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04518</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>metric_load_iris</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.05734</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.02333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.06335</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>metric_load_wine</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.06852</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.02192</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.08989999999999999</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0309</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>indices_PC_LabelCorrection_before_fix_OCPC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>0.072265</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.000109138725</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.01044694811894843</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>indices_CL_before_fix_OCPC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>0.09682499999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.631187500000003e-05</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.004038796231552173</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>indices_PC_LabelCorrection_after_fix_OCPC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>0.02245166666666666</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0003653303472222222</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.01911361680117665</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>indices_CL_after_fix_OCPC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>0.04006833333333334</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001262232880555556</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.03552791691832714</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>metric_2D</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.06387</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.05544</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.10395</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>metric_breast_cancer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.08892</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.03215</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0984</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.04499</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>metric_load_iris</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.10801</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.04134</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.06533</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>metric_load_wine</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.11012</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.04607</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.08989999999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.02866</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>indices_PC_LabelCorrection_before_fix_LOF</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>0.09272999999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.00034582655</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.01859641228839585</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>indices_CL_before_fix_LOF</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>0.09682499999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.631187500000003e-05</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.004038796231552173</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>indices_PC_LabelCorrection_after_fix_LOF</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0.02916666666666666</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.000472414988888889</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.02173510958999032</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>indices_CL_after_fix_LOF</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LOF</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>0.04048833333333333</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.001347212713888889</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.03670439638366076</v>
+        <v>0.09405940594059406</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.0891089108910891</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -553,11 +553,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>LOF</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.007425742574257425</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08415841584158416</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -628,11 +628,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>LOF</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04950495049504951</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09405940594059406</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -650,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0891089108910891</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.007425742574257425</v>
+        <v>0.008970544484396506</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>8.726387788087743e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.002954046003041886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09900990099009901</v>
+        <v>0.08847281204789581</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3.085423640522228e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.005554658981901795</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>18.75</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>163.1875</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12.77448629104122</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.6186011904761904</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.07266747714710885</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.2695690582153464</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.3813988095238095</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.07266747714710883</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.2695690582153464</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>20.1875</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.493050188902857</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.01633116776261659</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.0002244676654451156</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.01498224500684445</v>
       </c>
     </row>
     <row r="3">
@@ -632,67 +632,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0124648341594097</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.0001075135586481972</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.01036887451212508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09900990099009901</v>
+        <v>0.07338950349587595</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.0002666787127039868</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.01633030044745003</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>327.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>18.09696107085386</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.8584821428571429</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.01510423309948979</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.1228992803050115</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.1415178571428571</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.0151042330994898</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.1228992803050115</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>6.96419413859206</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.03510827853583724</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.0006746632738014887</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.02597428100643959</v>
       </c>
     </row>
   </sheetData>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.008970544484396506</v>
+        <v>0.003783025051187017</v>
       </c>
       <c r="D2" t="n">
-        <v>8.726387788087743e-06</v>
+        <v>6.015381026614861e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002954046003041886</v>
+        <v>0.002452627372149072</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08847281204789581</v>
+        <v>0.09056627207516471</v>
       </c>
       <c r="G2" t="n">
-        <v>3.085423640522228e-05</v>
+        <v>5.447441833173302e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005554658981901795</v>
+        <v>0.007380678717552542</v>
       </c>
       <c r="I2" t="n">
-        <v>18.75</v>
+        <v>17.25</v>
       </c>
       <c r="J2" t="n">
-        <v>163.1875</v>
+        <v>123.6875</v>
       </c>
       <c r="K2" t="n">
-        <v>12.77448629104122</v>
+        <v>11.12148820976761</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6186011904761904</v>
+        <v>0.596875</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07266747714710885</v>
+        <v>0.069716796875</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2695690582153464</v>
+        <v>0.2640393850829834</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3813988095238095</v>
+        <v>0.403125</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07266747714710883</v>
+        <v>0.06971679687499999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2695690582153464</v>
+        <v>0.2640393850829834</v>
       </c>
       <c r="R2" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>20.1875</v>
+        <v>24.6875</v>
       </c>
       <c r="T2" t="n">
-        <v>4.493050188902857</v>
+        <v>4.968651728587948</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01633116776261659</v>
+        <v>0.01817502945571112</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002244676654451156</v>
+        <v>0.0002969592926993967</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01498224500684445</v>
+        <v>0.01723250686056433</v>
       </c>
     </row>
     <row r="3">
@@ -632,67 +632,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0124648341594097</v>
+        <v>0.008964630206430135</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001075135586481972</v>
+        <v>4.742415363067375e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01036887451212508</v>
+        <v>0.006886519703788971</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07338950349587595</v>
+        <v>0.07549328792992646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002666787127039868</v>
+        <v>0.0002212880633713741</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01633030044745003</v>
+        <v>0.01487575421185004</v>
       </c>
       <c r="I3" t="n">
-        <v>29</v>
+        <v>30.25</v>
       </c>
       <c r="J3" t="n">
-        <v>327.5</v>
+        <v>267.1875</v>
       </c>
       <c r="K3" t="n">
-        <v>18.09696107085386</v>
+        <v>16.34587103827753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8584821428571429</v>
+        <v>0.9488095238095238</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01510423309948979</v>
+        <v>0.003099489795918365</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1228992803050115</v>
+        <v>0.05567306167185675</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1415178571428571</v>
+        <v>0.05119047619047619</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0151042330994898</v>
+        <v>0.003099489795918367</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1228992803050115</v>
+        <v>0.05567306167185677</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="S3" t="n">
-        <v>48.5</v>
+        <v>51.1875</v>
       </c>
       <c r="T3" t="n">
-        <v>6.96419413859206</v>
+        <v>7.154544010627093</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03510827853583724</v>
+        <v>0.02980551051688964</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0006746632738014887</v>
+        <v>4.255973984858367e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02597428100643959</v>
+        <v>0.00652378263345612</v>
       </c>
     </row>
   </sheetData>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.003783025051187017</v>
+        <v>0.008275664561183711</v>
       </c>
       <c r="D2" t="n">
-        <v>6.015381026614861e-06</v>
+        <v>3.033647192574137e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002452627372149072</v>
+        <v>0.005507855474296813</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09056627207516471</v>
+        <v>0.08607363256516801</v>
       </c>
       <c r="G2" t="n">
-        <v>5.447441833173302e-05</v>
+        <v>0.0001416617253175578</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007380678717552542</v>
+        <v>0.0119021731342456</v>
       </c>
       <c r="I2" t="n">
-        <v>17.25</v>
+        <v>17.5</v>
       </c>
       <c r="J2" t="n">
-        <v>123.6875</v>
+        <v>120.75</v>
       </c>
       <c r="K2" t="n">
-        <v>11.12148820976761</v>
+        <v>10.98863048791796</v>
       </c>
       <c r="L2" t="n">
-        <v>0.596875</v>
+        <v>0.5894345238095238</v>
       </c>
       <c r="M2" t="n">
-        <v>0.069716796875</v>
+        <v>0.07920393548044219</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2640393850829834</v>
+        <v>0.2814319375629606</v>
       </c>
       <c r="O2" t="n">
-        <v>0.403125</v>
+        <v>0.4105654761904762</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06971679687499999</v>
+        <v>0.07920393548044216</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2640393850829834</v>
+        <v>0.2814319375629606</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>24.6875</v>
+        <v>23.5</v>
       </c>
       <c r="T2" t="n">
-        <v>4.968651728587948</v>
+        <v>4.847679857416329</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01817502945571112</v>
+        <v>0.01677053507368865</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002969592926993967</v>
+        <v>0.0002276838736095813</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01723250686056433</v>
+        <v>0.0150891972486803</v>
       </c>
     </row>
     <row r="3">
@@ -632,67 +632,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.008964630206430135</v>
+        <v>0.007904201470481757</v>
       </c>
       <c r="D3" t="n">
-        <v>4.742415363067375e-05</v>
+        <v>4.995824697640136e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006886519703788971</v>
+        <v>0.007068114810640908</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07549328792992646</v>
+        <v>0.07267255956850993</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002212880633713741</v>
+        <v>0.000518289969752389</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01487575421185004</v>
+        <v>0.02276598273197072</v>
       </c>
       <c r="I3" t="n">
-        <v>30.25</v>
+        <v>29.5</v>
       </c>
       <c r="J3" t="n">
-        <v>267.1875</v>
+        <v>278.25</v>
       </c>
       <c r="K3" t="n">
-        <v>16.34587103827753</v>
+        <v>16.68082731761228</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9488095238095238</v>
+        <v>0.9133928571428571</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003099489795918365</v>
+        <v>0.009555963010204081</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05567306167185675</v>
+        <v>0.09775460608178052</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05119047619047619</v>
+        <v>0.08660714285714285</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003099489795918367</v>
+        <v>0.009555963010204081</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05567306167185677</v>
+        <v>0.09775460608178052</v>
       </c>
       <c r="R3" t="n">
-        <v>10.25</v>
+        <v>9.25</v>
       </c>
       <c r="S3" t="n">
-        <v>51.1875</v>
+        <v>64.1875</v>
       </c>
       <c r="T3" t="n">
-        <v>7.154544010627093</v>
+        <v>8.011710179481033</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02980551051688964</v>
+        <v>0.02636513592118675</v>
       </c>
       <c r="V3" t="n">
-        <v>4.255973984858367e-05</v>
+        <v>0.0001172931289289076</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00652378263345612</v>
+        <v>0.01083019523964862</v>
       </c>
     </row>
   </sheetData>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.008275664561183711</v>
+        <v>0.009063596605706265</v>
       </c>
       <c r="D2" t="n">
-        <v>3.033647192574137e-05</v>
+        <v>2.838675874500339e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005507855474296813</v>
+        <v>0.005327922554336107</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08607363256516801</v>
+        <v>0.08528570052064546</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001416617253175578</v>
+        <v>8.418433483566089e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0119021731342456</v>
+        <v>0.009175202168653336</v>
       </c>
       <c r="I2" t="n">
-        <v>17.5</v>
+        <v>18.25</v>
       </c>
       <c r="J2" t="n">
-        <v>120.75</v>
+        <v>93.1875</v>
       </c>
       <c r="K2" t="n">
-        <v>10.98863048791796</v>
+        <v>9.653367288153911</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5894345238095238</v>
+        <v>0.6334821428571429</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07920393548044219</v>
+        <v>0.04425601881377551</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2814319375629606</v>
+        <v>0.210371145392555</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4105654761904762</v>
+        <v>0.3665178571428572</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07920393548044216</v>
+        <v>0.04425601881377551</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2814319375629606</v>
+        <v>0.210371145392555</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="S2" t="n">
-        <v>23.5</v>
+        <v>51.6875</v>
       </c>
       <c r="T2" t="n">
-        <v>4.847679857416329</v>
+        <v>7.189401922274203</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01677053507368865</v>
+        <v>0.02081123332214346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0002276838736095813</v>
+        <v>0.0003331749725345255</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0150891972486803</v>
+        <v>0.01825308117920165</v>
       </c>
     </row>
     <row r="3">
@@ -632,67 +632,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.007904201470481757</v>
+        <v>0.007124433247613776</v>
       </c>
       <c r="D3" t="n">
-        <v>4.995824697640136e-05</v>
+        <v>1.333756486591003e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007068114810640908</v>
+        <v>0.001154883754579223</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07267255956850993</v>
+        <v>0.08487814078301652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000518289969752389</v>
+        <v>8.24060133176483e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02276598273197072</v>
+        <v>0.009077775791329521</v>
       </c>
       <c r="I3" t="n">
-        <v>29.5</v>
+        <v>29.75</v>
       </c>
       <c r="J3" t="n">
-        <v>278.25</v>
+        <v>239.1875</v>
       </c>
       <c r="K3" t="n">
-        <v>16.68082731761228</v>
+        <v>15.46568782822154</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9133928571428571</v>
+        <v>0.9485119047619048</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009555963010204081</v>
+        <v>0.001078071853741497</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09775460608178052</v>
+        <v>0.0328340045340421</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08660714285714285</v>
+        <v>0.05148809523809524</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009555963010204081</v>
+        <v>0.001078071853741497</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09775460608178052</v>
+        <v>0.0328340045340421</v>
       </c>
       <c r="R3" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>64.1875</v>
+        <v>41</v>
       </c>
       <c r="T3" t="n">
-        <v>8.011710179481033</v>
+        <v>6.403124237432849</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02636513592118675</v>
+        <v>0.03224753527760904</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001172931289289076</v>
+        <v>0.0001173842466040383</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01083019523964862</v>
+        <v>0.0108344010726961</v>
       </c>
     </row>
   </sheetData>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.009063596605706265</v>
+        <v>0.00493200682106875</v>
       </c>
       <c r="D2" t="n">
-        <v>2.838675874500339e-05</v>
+        <v>2.72972741832992e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005327922554336107</v>
+        <v>0.005224679337844496</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08528570052064546</v>
+        <v>0.08941729030528298</v>
       </c>
       <c r="G2" t="n">
-        <v>8.418433483566089e-05</v>
+        <v>0.0001594742835685302</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009175202168653336</v>
+        <v>0.01262831277600179</v>
       </c>
       <c r="I2" t="n">
-        <v>18.25</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
-        <v>93.1875</v>
+        <v>118.5</v>
       </c>
       <c r="K2" t="n">
-        <v>9.653367288153911</v>
+        <v>10.88577052853862</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6334821428571429</v>
+        <v>0.6654761904761906</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04425601881377551</v>
+        <v>0.07436437074829934</v>
       </c>
       <c r="N2" t="n">
-        <v>0.210371145392555</v>
+        <v>0.2726983145314605</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3665178571428572</v>
+        <v>0.3345238095238095</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04425601881377551</v>
+        <v>0.07436437074829931</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.210371145392555</v>
+        <v>0.2726983145314604</v>
       </c>
       <c r="R2" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="S2" t="n">
-        <v>51.6875</v>
+        <v>19.25</v>
       </c>
       <c r="T2" t="n">
-        <v>7.189401922274203</v>
+        <v>4.387482193696061</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02081123332214346</v>
+        <v>0.01492667338059412</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0003331749725345255</v>
+        <v>0.0001657936953300063</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01825308117920165</v>
+        <v>0.01287609006375795</v>
       </c>
     </row>
     <row r="3">
@@ -632,67 +632,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.007124433247613776</v>
+        <v>0.008091809862252393</v>
       </c>
       <c r="D3" t="n">
-        <v>1.333756486591003e-06</v>
+        <v>1.445357485392214e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001154883754579223</v>
+        <v>0.00380178574539941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08487814078301652</v>
+        <v>0.08874971886813687</v>
       </c>
       <c r="G3" t="n">
-        <v>8.24060133176483e-05</v>
+        <v>4.656018438181574e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009077775791329521</v>
+        <v>0.006823502354496241</v>
       </c>
       <c r="I3" t="n">
-        <v>29.75</v>
+        <v>31</v>
       </c>
       <c r="J3" t="n">
-        <v>239.1875</v>
+        <v>280.5</v>
       </c>
       <c r="K3" t="n">
-        <v>15.46568782822154</v>
+        <v>16.74813422444423</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9485119047619048</v>
+        <v>0.9754464285714286</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001078071853741497</v>
+        <v>0.0006925621811224489</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0328340045340421</v>
+        <v>0.02631657616640981</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05148809523809524</v>
+        <v>0.02455357142857143</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001078071853741497</v>
+        <v>0.0006925621811224489</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0328340045340421</v>
+        <v>0.02631657616640981</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="S3" t="n">
-        <v>41</v>
+        <v>39.1875</v>
       </c>
       <c r="T3" t="n">
-        <v>6.403124237432849</v>
+        <v>6.259992012774457</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03224753527760904</v>
+        <v>0.02434549439225434</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001173842466040383</v>
+        <v>4.52180269299886e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0108344010726961</v>
+        <v>0.00672443506400267</v>
       </c>
     </row>
   </sheetData>

--- a/tests/global_metrics.xlsx
+++ b/tests/global_metrics.xlsx
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.00493200682106875</v>
+        <v>0.009243041175822328</v>
       </c>
       <c r="D2" t="n">
-        <v>2.72972741832992e-05</v>
+        <v>3.345665044950566e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005224679337844496</v>
+        <v>0.005784172408348982</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08941729030528298</v>
+        <v>0.0851062559505294</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001594742835685302</v>
+        <v>8.850496365223234e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01262831277600179</v>
+        <v>0.00940770767255405</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>16.75</v>
       </c>
       <c r="J2" t="n">
-        <v>118.5</v>
+        <v>98.1875</v>
       </c>
       <c r="K2" t="n">
-        <v>10.88577052853862</v>
+        <v>9.908960591303208</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6654761904761906</v>
+        <v>0.5703869047619048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07436437074829934</v>
+        <v>0.04751919908588435</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2726983145314605</v>
+        <v>0.2179889884509865</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3345238095238095</v>
+        <v>0.4296130952380952</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07436437074829931</v>
+        <v>0.04751919908588435</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2726983145314604</v>
+        <v>0.2179889884509866</v>
       </c>
       <c r="R2" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>19.25</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>4.387482193696061</v>
+        <v>5.612486080160912</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01492667338059412</v>
+        <v>0.02142338553082812</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001657936953300063</v>
+        <v>0.0004716889477718434</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01287609006375795</v>
+        <v>0.02171840113295275</v>
       </c>
     </row>
     <row r="3">
@@ -632,67 +632,67 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.008091809862252393</v>
+        <v>0.02457086813714842</v>
       </c>
       <c r="D3" t="n">
-        <v>1.445357485392214e-05</v>
+        <v>0.0008420404201825649</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00380178574539941</v>
+        <v>0.02901793273447585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08874971886813687</v>
+        <v>0.07899207669231606</v>
       </c>
       <c r="G3" t="n">
-        <v>4.656018438181574e-05</v>
+        <v>0.0002706789141995613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006823502354496241</v>
+        <v>0.0164523224561021</v>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>280.5</v>
+        <v>288.5</v>
       </c>
       <c r="K3" t="n">
-        <v>16.74813422444423</v>
+        <v>16.98528775146303</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9754464285714286</v>
+        <v>0.9296130952380952</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006925621811224489</v>
+        <v>0.0014105681335034</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02631657616640981</v>
+        <v>0.037557530982526</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02455357142857143</v>
+        <v>0.07038690476190476</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0006925621811224489</v>
+        <v>0.001410568133503401</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02631657616640981</v>
+        <v>0.03755753098252601</v>
       </c>
       <c r="R3" t="n">
-        <v>8.25</v>
+        <v>13.25</v>
       </c>
       <c r="S3" t="n">
-        <v>39.1875</v>
+        <v>27.1875</v>
       </c>
       <c r="T3" t="n">
-        <v>6.259992012774457</v>
+        <v>5.214163403653552</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02434549439225434</v>
+        <v>0.05008167194259365</v>
       </c>
       <c r="V3" t="n">
-        <v>4.52180269299886e-05</v>
+        <v>0.001071145459890524</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00672443506400267</v>
+        <v>0.0327283586495034</v>
       </c>
     </row>
   </sheetData>
